--- a/data/trans_dic/P56$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,84</t>
+          <t>0,0; 57,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 33,15</t>
+          <t>4,52; 37,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,87</t>
+          <t>0,0; 37,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,28</t>
+          <t>0,0; 74,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 31,94</t>
+          <t>3,48; 30,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,78</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,47</t>
+          <t>0,0; 44,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,71</t>
+          <t>0,0; 40,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,93</t>
+          <t>0,0; 16,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,01</t>
+          <t>1,36; 11,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,56</t>
+          <t>0,0; 31,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 15,15</t>
+          <t>1,88; 17,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,8</t>
+          <t>1,04; 8,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,06</t>
+          <t>0,0; 18,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,46</t>
+          <t>0,0; 54,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 17,4</t>
+          <t>2,94; 16,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 36,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,76</t>
+          <t>2,36; 13,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,79</t>
+          <t>0,0; 32,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,39</t>
+          <t>0,0; 60,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,14</t>
+          <t>0,0; 28,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 60,63</t>
+          <t>17,21; 60,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,82</t>
+          <t>0,0; 11,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,2</t>
+          <t>0,0; 42,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,39</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 45,21</t>
+          <t>11,82; 46,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 41,16</t>
+          <t>5,53; 42,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,16</t>
+          <t>0,0; 37,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 15,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 33,4</t>
+          <t>4,12; 33,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,26</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 9,46</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,53</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 27,2</t>
+          <t>5,16; 26,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 38,61</t>
+          <t>0,0; 38,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 16,61</t>
+          <t>4,45; 17,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 34,05</t>
+          <t>5,54; 35,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 17,39</t>
+          <t>6,01; 16,99</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 46,54</t>
+          <t>4,86; 46,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,53</t>
+          <t>0,0; 36,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 33,8</t>
+          <t>8,76; 34,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,33</t>
+          <t>0,47; 10,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,61</t>
+          <t>0,0; 40,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 31,61</t>
+          <t>9,63; 32,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,61</t>
+          <t>1,68; 11,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 40,22</t>
+          <t>4,34; 39,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,64</t>
+          <t>0,0; 14,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,01</t>
+          <t>0,0; 26,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 26,85</t>
+          <t>3,58; 31,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 48,76</t>
+          <t>5,82; 45,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,47</t>
+          <t>0,9; 7,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 23,14</t>
+          <t>4,89; 23,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 21,95</t>
+          <t>2,68; 23,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 32,27</t>
+          <t>4,13; 33,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,22</t>
+          <t>0,7; 7,08</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,29</t>
+          <t>1,92; 15,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 18,46</t>
+          <t>2,62; 17,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,49</t>
+          <t>2,72; 9,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,21</t>
+          <t>5,12; 19,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,72</t>
+          <t>3,65; 10,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,35; 23,44</t>
+          <t>10,85; 24,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,63</t>
+          <t>3,03; 6,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,49</t>
+          <t>5,49; 14,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,75</t>
+          <t>3,23; 8,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,94; 19,5</t>
+          <t>9,75; 19,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,6</t>
+          <t>3,41; 6,71</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1276</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4079</t>
+          <t>0; 4034</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1441</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>956; 7040</t>
+          <t>960; 8023</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6412</t>
+          <t>0; 6857</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3746</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>986; 9035</t>
+          <t>984; 8679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7019</t>
+          <t>0; 6297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1096</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1599</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4739</t>
+          <t>0; 5257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1449</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1538</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>0; 5885</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6618</t>
+          <t>0; 6019</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2404</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>574; 4614</t>
+          <t>570; 4962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6814</t>
+          <t>0; 6798</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>899; 7366</t>
+          <t>914; 8510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2212</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>581; 4764</t>
+          <t>563; 4781</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1397</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5693</t>
+          <t>0; 6656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2236</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>987; 5830</t>
+          <t>984; 5655</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5228</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1443; 6615</t>
+          <t>1223; 6935</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1802</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1570</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2393</t>
+          <t>0; 2989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6639</t>
+          <t>0; 6495</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6095</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3893; 15112</t>
+          <t>4290; 15163</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2139</t>
+          <t>0; 2293</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6589</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5725</t>
+          <t>0; 5015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4039; 15791</t>
+          <t>4129; 16325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3527</t>
+          <t>0; 3211</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1309</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 887</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>907; 8107</t>
+          <t>1090; 8317</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6560</t>
+          <t>0; 4601</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2599</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1783</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1097; 8821</t>
+          <t>1088; 8929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5457</t>
+          <t>0; 5222</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2326</t>
+          <t>0; 2278</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1336</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1819</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4922</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>793; 4496</t>
+          <t>852; 4420</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>950; 8535</t>
+          <t>0; 8446</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1497; 5275</t>
+          <t>1414; 5542</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1922; 11209</t>
+          <t>1825; 11592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2973; 8397</t>
+          <t>2903; 8204</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1370</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>959; 9284</t>
+          <t>969; 9317</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4532</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3338; 14502</t>
+          <t>3758; 14938</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>162; 4332</t>
+          <t>198; 4227</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3711</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6233; 19869</t>
+          <t>6054; 20370</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>958; 6853</t>
+          <t>915; 6460</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>848; 7726</t>
+          <t>834; 7597</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2629</t>
+          <t>0; 2929</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7487</t>
+          <t>0; 7784</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1065; 8073</t>
+          <t>1076; 9609</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1355; 11098</t>
+          <t>1324; 10280</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>504; 4284</t>
+          <t>518; 4288</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2474; 11373</t>
+          <t>2405; 11460</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1069; 8548</t>
+          <t>1043; 9204</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1329; 10283</t>
+          <t>1315; 10640</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>548; 5638</t>
+          <t>545; 5532</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>928; 7867</t>
+          <t>929; 7709</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 7218</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1821; 13312</t>
+          <t>1886; 12832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2819; 9681</t>
+          <t>2775; 9954</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5358; 18907</t>
+          <t>4787; 18084</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7240; 22002</t>
+          <t>7495; 21985</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17776; 40263</t>
+          <t>18642; 41348</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7666; 16643</t>
+          <t>7607; 17087</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7614; 21970</t>
+          <t>7792; 21243</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8668; 24828</t>
+          <t>9166; 24381</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24249; 47560</t>
+          <t>23786; 47572</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11872; 23313</t>
+          <t>12036; 23709</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Provincia-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,21</t>
+          <t>0,0; 57,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 37,78</t>
+          <t>4,52; 33,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,29</t>
+          <t>0,0; 36,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,02</t>
+          <t>0,0; 73,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 30,68</t>
+          <t>3,44; 31,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 25,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,89</t>
+          <t>0,0; 40,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,02</t>
+          <t>0,0; 43,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,31</t>
+          <t>0,0; 16,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,84</t>
+          <t>1,34; 10,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,49</t>
+          <t>0,0; 33,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 17,5</t>
+          <t>1,83; 16,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,83</t>
+          <t>1,02; 8,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,08</t>
+          <t>0,0; 20,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,32</t>
+          <t>0,0; 42,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,87</t>
+          <t>3,03; 16,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,26</t>
+          <t>0,0; 36,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,38</t>
+          <t>3,04; 13,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,22</t>
+          <t>0,0; 25,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,07</t>
+          <t>0,0; 58,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,1</t>
+          <t>0,0; 25,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 60,84</t>
+          <t>15,01; 59,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,6</t>
+          <t>0,0; 10,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,13</t>
+          <t>0,0; 48,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,1</t>
+          <t>0,0; 18,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 46,74</t>
+          <t>11,96; 45,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 10,52</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 42,22</t>
+          <t>5,44; 43,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,98</t>
+          <t>0,0; 43,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 33,81</t>
+          <t>3,69; 34,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 41,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 10,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>0,0; 44,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 26,75</t>
+          <t>4,94; 26,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,21</t>
+          <t>4,14; 35,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 17,45</t>
+          <t>4,41; 18,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 35,21</t>
+          <t>5,43; 33,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 16,99</t>
+          <t>6,1; 17,89</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 46,71</t>
+          <t>4,96; 47,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,97</t>
+          <t>0,0; 37,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1587,17 +1587,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 34,82</t>
+          <t>7,9; 34,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,08</t>
+          <t>1,27; 12,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,18</t>
+          <t>0,0; 40,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 32,41</t>
+          <t>9,87; 31,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,89</t>
+          <t>2,11; 12,33</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 39,54</t>
+          <t>4,34; 41,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1712,47 +1712,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,08</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,01</t>
+          <t>0,0; 23,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 31,96</t>
+          <t>3,53; 30,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 45,17</t>
+          <t>5,73; 44,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,48</t>
+          <t>0,88; 7,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 23,32</t>
+          <t>5,03; 23,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 23,63</t>
+          <t>2,79; 23,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,13; 33,39</t>
+          <t>4,07; 34,94</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,08</t>
+          <t>0,69; 6,89</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,97</t>
+          <t>1,93; 16,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,8</t>
+          <t>3,2; 16,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,75</t>
+          <t>2,71; 9,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 19,33</t>
+          <t>4,9; 18,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,71</t>
+          <t>3,64; 10,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,07</t>
+          <t>11,01; 23,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,81</t>
+          <t>3,12; 6,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,98</t>
+          <t>5,42; 15,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,59</t>
+          <t>3,15; 8,49</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,51</t>
+          <t>9,5; 19,46</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,71</t>
+          <t>3,41; 6,72</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4034</t>
+          <t>0; 4031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>960; 8023</t>
+          <t>961; 7044</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6857</t>
+          <t>0; 6693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>984; 8679</t>
+          <t>973; 8999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6297</t>
+          <t>0; 7292</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1833</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5257</t>
+          <t>0; 4696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5885</t>
+          <t>0; 6329</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6019</t>
+          <t>0; 5963</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>570; 4962</t>
+          <t>597; 4894</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6798</t>
+          <t>0; 7281</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>914; 8510</t>
+          <t>892; 8115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>563; 4781</t>
+          <t>591; 4799</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3283</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>0; 3652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6656</t>
+          <t>0; 5265</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>984; 5655</t>
+          <t>1018; 5477</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 5527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1223; 6935</t>
+          <t>1565; 6756</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>420</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1008</t>
         </is>
       </c>
     </row>
@@ -2848,47 +2848,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2989</t>
+          <t>0; 2452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6495</t>
+          <t>0; 6314</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6311</t>
+          <t>0; 5806</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4290; 15163</t>
+          <t>3740; 14894</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2293</t>
+          <t>0; 2218</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5643</t>
+          <t>0; 6437</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5015</t>
+          <t>0; 5843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4129; 16325</t>
+          <t>4178; 16057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3211</t>
+          <t>0; 3192</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>781</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>781</t>
         </is>
       </c>
     </row>
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1090; 8317</t>
+          <t>1071; 8491</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4601</t>
+          <t>0; 5265</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2417</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1088; 8929</t>
+          <t>974; 9183</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5222</t>
+          <t>0; 5310</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2278</t>
+          <t>0; 2619</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5357</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3259,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>0; 4859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>852; 4420</t>
+          <t>818; 4382</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 8446</t>
+          <t>916; 7936</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1414; 5542</t>
+          <t>1436; 5894</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1825; 11592</t>
+          <t>1788; 10998</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2903; 8204</t>
+          <t>2996; 8787</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3901</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>969; 9317</t>
+          <t>990; 9513</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>0; 5604</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3758; 14938</t>
+          <t>3387; 14956</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>198; 4227</t>
+          <t>654; 6289</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3673</t>
+          <t>0; 3715</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6054; 20370</t>
+          <t>6202; 19921</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>915; 6460</t>
+          <t>1402; 8204</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2480</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>834; 7597</t>
+          <t>834; 8038</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3680,47 +3680,47 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2929</t>
+          <t>0; 2895</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7784</t>
+          <t>0; 6979</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1076; 9609</t>
+          <t>1062; 9105</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1324; 10280</t>
+          <t>1305; 10178</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>518; 4288</t>
+          <t>584; 4776</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2405; 11460</t>
+          <t>2474; 11359</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1043; 9204</t>
+          <t>1087; 9196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1315; 10640</t>
+          <t>1296; 11132</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>545; 5532</t>
+          <t>625; 6219</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>929; 7709</t>
+          <t>930; 7811</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 7218</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1886; 12832</t>
+          <t>2310; 12109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2775; 9954</t>
+          <t>2947; 10199</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4787; 18084</t>
+          <t>4581; 17262</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7495; 21985</t>
+          <t>7468; 22350</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18642; 41348</t>
+          <t>18906; 41034</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7607; 17087</t>
+          <t>8592; 19055</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7792; 21243</t>
+          <t>7687; 21536</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9166; 24381</t>
+          <t>8925; 24093</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23786; 47572</t>
+          <t>23168; 47464</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12036; 23709</t>
+          <t>13099; 25813</t>
         </is>
       </c>
     </row>
